--- a/deliverables/06-wrapup/CFU-000-PR-RPT-002_Preliminary-HAZOP.xlsx
+++ b/deliverables/06-wrapup/CFU-000-PR-RPT-002_Preliminary-HAZOP.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PID-001/002</t>
+          <t>PID-001</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PID-003</t>
+          <t>PID-002</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PID-004</t>
+          <t>PID-003</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PID-005</t>
+          <t>PID-004/005</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1299,27 +1299,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>N09</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Less temperature (reboiler)</t>
+          <t>Less level</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MP steam loss</t>
+          <t>LV/FV on LPG product fails open, LIC-1092 fault</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Off-spec LN/HN, no safety consequence</t>
+          <t>Gas blow-by into LPG treating, overpressure downstream</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TAL-1104; quality alarms</t>
+          <t>LALL-1092; SIF-109 closes XV-1093 (SIL 1)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1327,64 +1327,60 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Less flow / coking</t>
+          <t>Less temperature (reboiler)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Loss of coil steam, low pass flow</t>
+          <t>MP steam loss</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tube coking, hot spots, rupture</t>
+          <t>Off-spec LN/HN, no safety consequence</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>FIC-2007 coil steam, SIF-201</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Online spalling / pigging provision</t>
-        </is>
-      </c>
+          <t>TAL-1104; quality alarms</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Air ingress</t>
+          <t>Less flow / coking</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Flange leak under vacuum</t>
+          <t>Loss of coil steam, low pass flow</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Internal fire / explosion in column, loss of vacuum</t>
+          <t>Tube coking, hot spots, rupture</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>O2 analyser on off-gas, leak testing, tightness class, hot-oil temperature limits</t>
+          <t>FIC-2007 coil steam, SIF-201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Add O2 analyser AI-2032 on J-201 suction</t>
+          <t>Online spalling / pigging provision</t>
         </is>
       </c>
     </row>
@@ -1396,25 +1392,29 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Less flow (wash oil)</t>
+          <t>Air ingress</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FV-2020 fails closed</t>
+          <t>Flange leak under vacuum</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Wash-bed coking -&gt; HVGO metals/CCR off-spec, bed plugging</t>
+          <t>Internal fire / explosion in column, loss of vacuum</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>FAL-2020 (critical alarm), min-stop on FV-2020</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>O2 analyser on off-gas, leak testing, tightness class, hot-oil temperature limits</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Add O2 analyser AI-2032 on J-201 suction</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>More temperature (bottoms)</t>
+          <t>Less flow (wash oil)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Loss of quench</t>
+          <t>FV-2020 fails closed</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VR coking in boot, P-204 damage</t>
+          <t>Wash-bed coking -&gt; HVGO metals/CCR off-spec, bed plugging</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>TIC-2026 / FIC-2027, TAH-2026</t>
+          <t>FAL-2020 (critical alarm), min-stop on FV-2020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1447,34 +1447,30 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Loss of vacuum</t>
+          <t>More temperature (bottoms)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Motive steam failure, CW failure</t>
+          <t>Loss of quench</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Column pressure rise, off-spec, possible relief</t>
+          <t>VR coking in boot, P-204 damage</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>PAH-2010, alarm on motive steam P</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Vacuum-loss emergency procedure (reduce H-201 firing)</t>
-        </is>
-      </c>
+          <t>TIC-2026 / FIC-2027, TAH-2026</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1484,57 +1480,89 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>H2S release</t>
+          <t>Loss of vacuum</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Hotwell vent / off-gas line</t>
+          <t>Motive steam failure, CW failure</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toxic exposure</t>
+          <t>Column pressure rise, off-spec, possible relief</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Off-gas routed to H-201 burners with KO D-202; H2S detectors</t>
+          <t>PAH-2010, alarm on motive steam P</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Backup off-gas route to flare on H-201 trip</t>
+          <t>Vacuum-loss emergency procedure (reduce H-201 firing)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>N12</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>H2S release</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Hotwell vent / off-gas line</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Toxic exposure</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Off-gas routed to H-201 burners with KO D-202; H2S detectors</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Backup off-gas route to flare on H-201 trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>N13</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Liquid in fuel gas</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Upstream carry-over</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Burner flame-out / flooding</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>D-103 LAHH -&gt; SIF-102</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
